--- a/config.xlsx
+++ b/config.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\backup\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\ICBC_E-Stamp_Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC87E6CF-087B-436A-BCEC-C191CCA83E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE7C3CDC-AF63-40B7-87F6-44FB9C96AD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23100" yWindow="2565" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ICBC E-Stamp and Copy Tool" sheetId="1" r:id="rId1"/>
-    <sheet name="Bulk Copy ICBC Tool" sheetId="2" r:id="rId2"/>
+    <sheet name="Create ICBC Folder Tool" sheetId="2" r:id="rId2"/>
     <sheet name="Readme" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
   <si>
     <t>Producer Code</t>
   </si>
@@ -36,6 +36,48 @@
   </si>
   <si>
     <t>Two scripts included:</t>
+  </si>
+  <si>
+    <t>This script provides a one-click solution to apply a digital validation stamp to most ICBC policy documents. It automatically detects PDFs that look like policy documents and applies the ICBC digital validation stamp.</t>
+  </si>
+  <si>
+    <t>C:\Users\&lt;USERNAME&gt;\Desktop\New ICBC Copies</t>
+  </si>
+  <si>
+    <t>C:\Users\&lt;USERNAME&gt;\Desktop\OLD ICBC Copies</t>
+  </si>
+  <si>
+    <t>C:\Users\&lt;USERNAME&gt;\Desktop\NEW ICBC Copies</t>
+  </si>
+  <si>
+    <t>AA</t>
+  </si>
+  <si>
+    <t>BB</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>DD</t>
+  </si>
+  <si>
+    <t>EE</t>
+  </si>
+  <si>
+    <t>Alfa</t>
+  </si>
+  <si>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>Charlie</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>Echo</t>
   </si>
   <si>
     <r>
@@ -45,7 +87,51 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>bulk_copy_icbc_tool</t>
+      <t>icbc_e-stamp_and_copy_tool</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – Limited to stamping and copying 10 pdfs at a time.  It will check duplicates before stamping or copying.  It works as long as your policy documents are downloaded to the Download folder.</t>
+    </r>
+  </si>
+  <si>
+    <t>README: https://github.com/WebDevBernard/ICBC_E-Stamp_Tool</t>
+  </si>
+  <si>
+    <t>Highly recommended: Read the full README before running this tool.</t>
+  </si>
+  <si>
+    <t>Old ICBC Copies Folder</t>
+  </si>
+  <si>
+    <t>New ICBC Copies Folder</t>
+  </si>
+  <si>
+    <t>ICBC Copies Folder</t>
+  </si>
+  <si>
+    <t>If you accidentally moved the archive folder into a subfolder and ran the icbc_e-stamp_and_copy_tool, do not try to manually fix this folder.  Run the bulk_copy_icbc_tool to make a new folder from the ruined folder.</t>
+  </si>
+  <si>
+    <t>Do not manually create folders in your new ICBC copies folder. There is no need to manually archive files. The icbc_e-stamp_and_copy_tool includes a built-in auto-archiving feature that continuously archives all files after one year.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>create_icbc_folder_tool</t>
     </r>
     <r>
       <rPr>
@@ -67,95 +153,14 @@
     </r>
   </si>
   <si>
-    <t>This script provides a one-click solution to apply a digital validation stamp to most ICBC policy documents. It automatically detects PDFs that look like policy documents and applies the ICBC digital validation stamp.</t>
-  </si>
-  <si>
-    <t>C:\Users\&lt;USERNAME&gt;\Desktop\New ICBC Copies</t>
-  </si>
-  <si>
-    <t>C:\Users\&lt;USERNAME&gt;\Desktop\OLD ICBC Copies</t>
-  </si>
-  <si>
-    <t>C:\Users\&lt;USERNAME&gt;\Desktop\NEW ICBC Copies</t>
-  </si>
-  <si>
-    <t>AA</t>
-  </si>
-  <si>
-    <t>BB</t>
-  </si>
-  <si>
-    <t>CC</t>
-  </si>
-  <si>
-    <t>DD</t>
-  </si>
-  <si>
-    <t>EE</t>
-  </si>
-  <si>
-    <t>Alfa</t>
-  </si>
-  <si>
-    <t>Bravo</t>
-  </si>
-  <si>
-    <t>Charlie</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Echo</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>icbc_e-stamp_and_copy_tool</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> – Limited to stamping and copying 10 pdfs at a time.  It will check duplicates before stamping or copying.  It works as long as your policy documents are downloaded to the Download folder.</t>
-    </r>
-  </si>
-  <si>
-    <t>README: https://github.com/WebDevBernard/ICBC_E-Stamp_Tool</t>
-  </si>
-  <si>
-    <t>Highly recommended: Read the full README before running this tool.</t>
-  </si>
-  <si>
-    <t>Old ICBC Copies Folder</t>
-  </si>
-  <si>
-    <t>New ICBC Copies Folder</t>
-  </si>
-  <si>
-    <t>ICBC Copies Folder</t>
-  </si>
-  <si>
-    <t>If you accidentally moved the archive folder into a subfolder and ran the icbc_e-stamp_and_copy_tool, do not try to manually fix this folder.  Run the bulk_copy_icbc_tool to make a new folder from the ruined folder.</t>
-  </si>
-  <si>
-    <t>Do not manually create folders in your new ICBC copies folder. There is no need to manually archive files. The icbc_e-stamp_and_copy_tool includes a built-in auto-archiving feature that continuously archives all files after one year.</t>
+    <t xml:space="preserve">Agency Number used for Certificate Replacement </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,6 +224,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -282,7 +293,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -311,6 +322,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -625,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
@@ -635,58 +652,66 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75">
       <c r="A1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.75">
-      <c r="A2" s="7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="63">
+      <c r="A2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="11">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.75">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B3" s="7" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -706,18 +731,18 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75">
       <c r="A1" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75">
       <c r="A2" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75">
@@ -730,42 +755,42 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -783,12 +808,12 @@
   <sheetData>
     <row r="1" spans="1:1" s="4" customFormat="1" ht="18.75">
       <c r="A1" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="30">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -798,12 +823,12 @@
     </row>
     <row r="5" spans="1:1" ht="45">
       <c r="A5" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="30">
-      <c r="A6" s="5" t="s">
-        <v>3</v>
+      <c r="A6" s="13" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -811,17 +836,17 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="45">
       <c r="A10" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="30">
       <c r="A12" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\ICBC_E-Stamp_Tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE7C3CDC-AF63-40B7-87F6-44FB9C96AD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4744B051-597F-47C2-9FC9-09A7BE686BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23100" yWindow="2565" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ICBC E-Stamp and Copy Tool" sheetId="1" r:id="rId1"/>
@@ -662,9 +662,7 @@
       <c r="A2" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="11">
-        <v>99999</v>
-      </c>
+      <c r="B2" s="11"/>
     </row>
     <row r="3" spans="1:2" ht="15.75">
       <c r="A3" s="7" t="s">
